--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>64.04581</v>
+      </c>
+      <c r="C2">
+        <v>97.11372</v>
+      </c>
+      <c r="D2">
+        <v>82.19962</v>
+      </c>
+      <c r="E2">
+        <v>39.54319</v>
+      </c>
+      <c r="F2">
         <v>64.40694999999999</v>
       </c>
-      <c r="C2">
-        <v>64.04581</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>102.3002</v>
       </c>
-      <c r="E2">
-        <v>97.11372</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>103.8726</v>
       </c>
-      <c r="G2">
-        <v>82.19962</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>62.60453</v>
-      </c>
-      <c r="I2">
-        <v>39.54319</v>
       </c>
     </row>
     <row r="3">
@@ -442,25 +442,25 @@
         <v>55.97228</v>
       </c>
       <c r="C3">
+        <v>97.32319</v>
+      </c>
+      <c r="D3">
+        <v>81.21827</v>
+      </c>
+      <c r="E3">
+        <v>30.64309</v>
+      </c>
+      <c r="F3">
         <v>55.97228</v>
       </c>
-      <c r="D3">
+      <c r="G3">
         <v>102.9961</v>
       </c>
-      <c r="E3">
-        <v>97.32319</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>100.6922</v>
       </c>
-      <c r="G3">
-        <v>81.21827</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>43.24878</v>
-      </c>
-      <c r="I3">
-        <v>30.64309</v>
       </c>
     </row>
     <row r="4">
@@ -473,25 +473,25 @@
         <v>48.11715</v>
       </c>
       <c r="C4">
+        <v>97.87797999999999</v>
+      </c>
+      <c r="D4">
+        <v>79.51220000000001</v>
+      </c>
+      <c r="E4">
+        <v>28.04054</v>
+      </c>
+      <c r="F4">
         <v>48.11715</v>
       </c>
-      <c r="D4">
+      <c r="G4">
         <v>105.0398</v>
       </c>
-      <c r="E4">
-        <v>97.87797999999999</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>89.2683</v>
       </c>
-      <c r="G4">
-        <v>79.51220000000001</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>38.17567</v>
-      </c>
-      <c r="I4">
-        <v>28.04054</v>
       </c>
     </row>
     <row r="5">
@@ -504,25 +504,25 @@
         <v>60.5364</v>
       </c>
       <c r="C5">
+        <v>97.09119</v>
+      </c>
+      <c r="D5">
+        <v>81.11888</v>
+      </c>
+      <c r="E5">
+        <v>34.31517</v>
+      </c>
+      <c r="F5">
         <v>60.5364</v>
       </c>
-      <c r="D5">
+      <c r="G5">
         <v>102.9088</v>
       </c>
-      <c r="E5">
-        <v>97.09119</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>102.0979</v>
       </c>
-      <c r="G5">
-        <v>81.11888</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>45.72901</v>
-      </c>
-      <c r="I5">
-        <v>34.31517</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>63.42495</v>
+      </c>
+      <c r="C6">
+        <v>95.67496</v>
+      </c>
+      <c r="D6">
+        <v>79.41177</v>
+      </c>
+      <c r="E6">
+        <v>33.19149</v>
+      </c>
+      <c r="F6">
         <v>63.98872</v>
       </c>
-      <c r="C6">
-        <v>63.42495</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>100.5679</v>
       </c>
-      <c r="E6">
-        <v>95.67496</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>100</v>
       </c>
-      <c r="G6">
-        <v>79.41177</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>48.6052</v>
-      </c>
-      <c r="I6">
-        <v>33.19149</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>54.42514</v>
+      </c>
+      <c r="C7">
+        <v>98.02245000000001</v>
+      </c>
+      <c r="D7">
+        <v>82.80633</v>
+      </c>
+      <c r="E7">
+        <v>31.16382</v>
+      </c>
+      <c r="F7">
         <v>54.756</v>
       </c>
-      <c r="C7">
-        <v>54.42514</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>104.9172</v>
       </c>
-      <c r="E7">
-        <v>98.02245000000001</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>101.1858</v>
       </c>
-      <c r="G7">
-        <v>82.80633</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>42.63651</v>
-      </c>
-      <c r="I7">
-        <v>31.16382</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>66.13033</v>
+      </c>
+      <c r="C8">
+        <v>96.2963</v>
+      </c>
+      <c r="D8">
+        <v>83.39587</v>
+      </c>
+      <c r="E8">
+        <v>35.82367</v>
+      </c>
+      <c r="F8">
         <v>66.45213</v>
       </c>
-      <c r="C8">
-        <v>66.13033</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>101.0655</v>
       </c>
-      <c r="E8">
-        <v>96.2963</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>100.9381</v>
       </c>
-      <c r="G8">
-        <v>83.39587</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>51.04408</v>
-      </c>
-      <c r="I8">
-        <v>35.82367</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>58.19761</v>
+      </c>
+      <c r="C9">
+        <v>96.26105</v>
+      </c>
+      <c r="D9">
+        <v>83.31303</v>
+      </c>
+      <c r="E9">
+        <v>29.86023</v>
+      </c>
+      <c r="F9">
         <v>58.30619</v>
       </c>
-      <c r="C9">
-        <v>58.19761</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>100.8838</v>
       </c>
-      <c r="E9">
-        <v>96.26105</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>104.7503</v>
       </c>
-      <c r="G9">
-        <v>83.31303</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>42.43964</v>
-      </c>
-      <c r="I9">
-        <v>29.86023</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>56.17374</v>
+      </c>
+      <c r="C10">
+        <v>95.76224999999999</v>
+      </c>
+      <c r="D10">
+        <v>83.45837</v>
+      </c>
+      <c r="E10">
+        <v>42.21377</v>
+      </c>
+      <c r="F10">
         <v>57.39385</v>
       </c>
-      <c r="C10">
-        <v>56.17374</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.3669</v>
       </c>
-      <c r="E10">
-        <v>95.76224999999999</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>97.96356</v>
       </c>
-      <c r="G10">
-        <v>83.45837</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>60.80865</v>
-      </c>
-      <c r="I10">
-        <v>42.21377</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>60.86695</v>
+      </c>
+      <c r="C11">
+        <v>96.32353000000001</v>
+      </c>
+      <c r="D11">
+        <v>82.50162</v>
+      </c>
+      <c r="E11">
+        <v>37.59426</v>
+      </c>
+      <c r="F11">
         <v>61.13787</v>
       </c>
-      <c r="C11">
-        <v>60.86695</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>101.5625</v>
       </c>
-      <c r="E11">
-        <v>96.32353000000001</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>106.5781</v>
       </c>
-      <c r="G11">
-        <v>82.50162</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>53.31985</v>
-      </c>
-      <c r="I11">
-        <v>37.59426</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>64.18277999999999</v>
+      </c>
+      <c r="C12">
+        <v>97.13168</v>
+      </c>
+      <c r="D12">
+        <v>81.83609</v>
+      </c>
+      <c r="E12">
+        <v>37.3636</v>
+      </c>
+      <c r="F12">
         <v>64.28822</v>
       </c>
-      <c r="C12">
-        <v>64.18277999999999</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>103.6071</v>
       </c>
-      <c r="E12">
-        <v>97.13168</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>112.0567</v>
       </c>
-      <c r="G12">
-        <v>81.83609</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>57.24574</v>
-      </c>
-      <c r="I12">
-        <v>37.3636</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>54.40313</v>
+      </c>
+      <c r="C13">
+        <v>96.3194</v>
+      </c>
+      <c r="D13">
+        <v>83.18680999999999</v>
+      </c>
+      <c r="E13">
+        <v>29.50609</v>
+      </c>
+      <c r="F13">
         <v>54.59883</v>
       </c>
-      <c r="C13">
-        <v>54.40313</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>101.8091</v>
       </c>
-      <c r="E13">
-        <v>96.3194</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>104.1758</v>
       </c>
-      <c r="G13">
-        <v>83.18680999999999</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>40.34637</v>
-      </c>
-      <c r="I13">
-        <v>29.50609</v>
       </c>
     </row>
     <row r="14">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>56.30631</v>
+      </c>
+      <c r="C14">
+        <v>97.29730000000001</v>
+      </c>
+      <c r="D14">
+        <v>82.32932</v>
+      </c>
+      <c r="E14">
+        <v>36.85567</v>
+      </c>
+      <c r="F14">
         <v>56.3063</v>
       </c>
-      <c r="C14">
-        <v>56.30631</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>103.6036</v>
       </c>
-      <c r="E14">
-        <v>97.29730000000001</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>92.77109</v>
       </c>
-      <c r="G14">
-        <v>82.32932</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>48.71134</v>
-      </c>
-      <c r="I14">
-        <v>36.85567</v>
       </c>
     </row>
     <row r="15">
@@ -814,25 +814,25 @@
         <v>57.69231</v>
       </c>
       <c r="C15">
+        <v>96.25908</v>
+      </c>
+      <c r="D15">
+        <v>85.18124</v>
+      </c>
+      <c r="E15">
+        <v>30.5136</v>
+      </c>
+      <c r="F15">
         <v>57.69231</v>
       </c>
-      <c r="D15">
+      <c r="G15">
         <v>101.005</v>
       </c>
-      <c r="E15">
-        <v>96.25908</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>109.5949</v>
       </c>
-      <c r="G15">
-        <v>85.18124</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>41.87311</v>
-      </c>
-      <c r="I15">
-        <v>30.5136</v>
       </c>
     </row>
     <row r="16">
@@ -845,25 +845,25 @@
         <v>58.59031</v>
       </c>
       <c r="C16">
+        <v>96.78283999999999</v>
+      </c>
+      <c r="D16">
+        <v>88.08511</v>
+      </c>
+      <c r="E16">
+        <v>32.31552</v>
+      </c>
+      <c r="F16">
         <v>58.59031</v>
       </c>
-      <c r="D16">
+      <c r="G16">
         <v>102.9491</v>
       </c>
-      <c r="E16">
-        <v>96.78283999999999</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>132.766</v>
       </c>
-      <c r="G16">
-        <v>88.08511</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>43.51145</v>
-      </c>
-      <c r="I16">
-        <v>32.31552</v>
       </c>
     </row>
     <row r="17">
@@ -876,25 +876,25 @@
         <v>55.67867</v>
       </c>
       <c r="C17">
+        <v>96.16027</v>
+      </c>
+      <c r="D17">
+        <v>87.53541</v>
+      </c>
+      <c r="E17">
+        <v>30.15598</v>
+      </c>
+      <c r="F17">
         <v>55.67867</v>
       </c>
-      <c r="D17">
+      <c r="G17">
         <v>103.3389</v>
       </c>
-      <c r="E17">
-        <v>96.16027</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>100.5666</v>
       </c>
-      <c r="G17">
-        <v>87.53541</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>40.03466</v>
-      </c>
-      <c r="I17">
-        <v>30.15598</v>
       </c>
     </row>
     <row r="18">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>53.63797</v>
+      </c>
+      <c r="C18">
+        <v>97.03579999999999</v>
+      </c>
+      <c r="D18">
+        <v>81.65989999999999</v>
+      </c>
+      <c r="E18">
+        <v>26.3593</v>
+      </c>
+      <c r="F18">
         <v>53.72671</v>
       </c>
-      <c r="C18">
-        <v>53.63797</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>103.4676</v>
       </c>
-      <c r="E18">
-        <v>97.03579999999999</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>108.2414</v>
       </c>
-      <c r="G18">
-        <v>81.65989999999999</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>37.58347</v>
-      </c>
-      <c r="I18">
-        <v>26.3593</v>
       </c>
     </row>
     <row r="19">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>52.74949</v>
+      </c>
+      <c r="C19">
+        <v>96.17769</v>
+      </c>
+      <c r="D19">
+        <v>87.69531000000001</v>
+      </c>
+      <c r="E19">
+        <v>27.13797</v>
+      </c>
+      <c r="F19">
         <v>52.95316</v>
       </c>
-      <c r="C19">
-        <v>52.74949</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>100.8264</v>
       </c>
-      <c r="E19">
-        <v>96.17769</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>103.9063</v>
       </c>
-      <c r="G19">
-        <v>87.69531000000001</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>36.71608</v>
-      </c>
-      <c r="I19">
-        <v>27.13797</v>
       </c>
     </row>
     <row r="20">
@@ -969,25 +969,25 @@
         <v>53.03983</v>
       </c>
       <c r="C20">
+        <v>95.58011999999999</v>
+      </c>
+      <c r="D20">
+        <v>81.40416999999999</v>
+      </c>
+      <c r="E20">
+        <v>33.36992</v>
+      </c>
+      <c r="F20">
         <v>53.03983</v>
       </c>
-      <c r="D20">
+      <c r="G20">
         <v>102.5414</v>
       </c>
-      <c r="E20">
-        <v>95.58011999999999</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>99.62049</v>
       </c>
-      <c r="G20">
-        <v>81.40416999999999</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>42.59056</v>
-      </c>
-      <c r="I20">
-        <v>33.36992</v>
       </c>
     </row>
     <row r="21">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>61.80763</v>
+      </c>
+      <c r="C21">
+        <v>96.57912</v>
+      </c>
+      <c r="D21">
+        <v>81.80061000000001</v>
+      </c>
+      <c r="E21">
+        <v>42.46957</v>
+      </c>
+      <c r="F21">
         <v>61.96979</v>
       </c>
-      <c r="C21">
-        <v>61.80763</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>103.1561</v>
       </c>
-      <c r="E21">
-        <v>96.57912</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>110.0881</v>
       </c>
-      <c r="G21">
-        <v>81.80061000000001</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>63.81353</v>
-      </c>
-      <c r="I21">
-        <v>42.46957</v>
       </c>
     </row>
     <row r="22">
@@ -1031,25 +1031,25 @@
         <v>51.63934</v>
       </c>
       <c r="C22">
+        <v>96.60523000000001</v>
+      </c>
+      <c r="D22">
+        <v>81.88824</v>
+      </c>
+      <c r="E22">
+        <v>28.95522</v>
+      </c>
+      <c r="F22">
         <v>51.63934</v>
       </c>
-      <c r="D22">
+      <c r="G22">
         <v>103.2978</v>
       </c>
-      <c r="E22">
-        <v>96.60523000000001</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>109.4412</v>
       </c>
-      <c r="G22">
-        <v>81.88824</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>39.00497</v>
-      </c>
-      <c r="I22">
-        <v>28.95522</v>
       </c>
     </row>
     <row r="23">
@@ -1059,28 +1059,28 @@
         </is>
       </c>
       <c r="B23">
+        <v>66.34282</v>
+      </c>
+      <c r="C23">
+        <v>96.76979</v>
+      </c>
+      <c r="D23">
+        <v>79.65065</v>
+      </c>
+      <c r="E23">
+        <v>37.46606</v>
+      </c>
+      <c r="F23">
         <v>66.48161</v>
       </c>
-      <c r="C23">
-        <v>66.34282</v>
-      </c>
-      <c r="D23">
+      <c r="G23">
         <v>104.4131</v>
       </c>
-      <c r="E23">
-        <v>96.76979</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>117.1179</v>
       </c>
-      <c r="G23">
-        <v>79.65065</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>54.75113</v>
-      </c>
-      <c r="I23">
-        <v>37.46606</v>
       </c>
     </row>
     <row r="24">
@@ -1093,25 +1093,25 @@
         <v>56.34589</v>
       </c>
       <c r="C24">
+        <v>96.31798999999999</v>
+      </c>
+      <c r="D24">
+        <v>84.39306999999999</v>
+      </c>
+      <c r="E24">
+        <v>32.85714</v>
+      </c>
+      <c r="F24">
         <v>56.34589</v>
       </c>
-      <c r="D24">
+      <c r="G24">
         <v>102.6778</v>
       </c>
-      <c r="E24">
-        <v>96.31798999999999</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>107.5145</v>
       </c>
-      <c r="G24">
-        <v>84.39306999999999</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>45.87302</v>
-      </c>
-      <c r="I24">
-        <v>32.85714</v>
       </c>
     </row>
     <row r="25">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>59.14315</v>
+      </c>
+      <c r="C25">
+        <v>97.53086999999999</v>
+      </c>
+      <c r="D25">
+        <v>80.33373</v>
+      </c>
+      <c r="E25">
+        <v>37.74295</v>
+      </c>
+      <c r="F25">
         <v>59.35214</v>
       </c>
-      <c r="C25">
-        <v>59.14315</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>102.859</v>
       </c>
-      <c r="E25">
-        <v>97.53086999999999</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>107.1514</v>
       </c>
-      <c r="G25">
-        <v>80.33373</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>54.85893</v>
-      </c>
-      <c r="I25">
-        <v>37.74295</v>
       </c>
     </row>
     <row r="26">
@@ -1155,25 +1155,25 @@
         <v>36.31436</v>
       </c>
       <c r="C26">
+        <v>96.86684</v>
+      </c>
+      <c r="D26">
+        <v>78.46154</v>
+      </c>
+      <c r="E26">
+        <v>26.68579</v>
+      </c>
+      <c r="F26">
         <v>36.31436</v>
       </c>
-      <c r="D26">
+      <c r="G26">
         <v>107.9634</v>
       </c>
-      <c r="E26">
-        <v>96.86684</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>99.78022</v>
       </c>
-      <c r="G26">
-        <v>78.46154</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>34.43328</v>
-      </c>
-      <c r="I26">
-        <v>26.68579</v>
       </c>
     </row>
     <row r="27">
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>55.60748</v>
+      </c>
+      <c r="C27">
+        <v>96.95480999999999</v>
+      </c>
+      <c r="D27">
+        <v>81.88976</v>
+      </c>
+      <c r="E27">
+        <v>37.89809</v>
+      </c>
+      <c r="F27">
         <v>55.919</v>
       </c>
-      <c r="C27">
-        <v>55.60748</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>104.6169</v>
       </c>
-      <c r="E27">
-        <v>96.95480999999999</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>101.8898</v>
       </c>
-      <c r="G27">
-        <v>81.88976</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>55.17516</v>
-      </c>
-      <c r="I27">
-        <v>37.89809</v>
       </c>
     </row>
     <row r="28">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="B28">
+        <v>45.74468</v>
+      </c>
+      <c r="C28">
+        <v>97.1831</v>
+      </c>
+      <c r="D28">
+        <v>87.5</v>
+      </c>
+      <c r="E28">
+        <v>32.09607</v>
+      </c>
+      <c r="F28">
         <v>46.4539</v>
       </c>
-      <c r="C28">
-        <v>45.74468</v>
-      </c>
-      <c r="D28">
+      <c r="G28">
         <v>102.6157</v>
       </c>
-      <c r="E28">
-        <v>97.1831</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>107.4219</v>
       </c>
-      <c r="G28">
-        <v>87.5</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>46.94323</v>
-      </c>
-      <c r="I28">
-        <v>32.09607</v>
       </c>
     </row>
     <row r="29">
@@ -1248,25 +1248,25 @@
         <v>51.31579</v>
       </c>
       <c r="C29">
+        <v>93.89830000000001</v>
+      </c>
+      <c r="D29">
+        <v>78.07017999999999</v>
+      </c>
+      <c r="E29">
+        <v>42.21312</v>
+      </c>
+      <c r="F29">
         <v>51.31579</v>
       </c>
-      <c r="D29">
+      <c r="G29">
         <v>102.7119</v>
       </c>
-      <c r="E29">
-        <v>93.89830000000001</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>107.8947</v>
       </c>
-      <c r="G29">
-        <v>78.07017999999999</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>47.95082</v>
-      </c>
-      <c r="I29">
-        <v>42.21312</v>
       </c>
     </row>
     <row r="30">
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B30">
+        <v>61.80451</v>
+      </c>
+      <c r="C30">
+        <v>96.49123</v>
+      </c>
+      <c r="D30">
+        <v>83.63047</v>
+      </c>
+      <c r="E30">
+        <v>32.69436</v>
+      </c>
+      <c r="F30">
         <v>61.95489</v>
       </c>
-      <c r="C30">
-        <v>61.80451</v>
-      </c>
-      <c r="D30">
+      <c r="G30">
         <v>105.4386</v>
       </c>
-      <c r="E30">
-        <v>96.49123</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>104.376</v>
       </c>
-      <c r="G30">
-        <v>83.63047</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>46.53887</v>
-      </c>
-      <c r="I30">
-        <v>32.69436</v>
       </c>
     </row>
     <row r="31">
@@ -1310,25 +1310,25 @@
         <v>66.45963</v>
       </c>
       <c r="C31">
+        <v>96.24413</v>
+      </c>
+      <c r="D31">
+        <v>78.22581</v>
+      </c>
+      <c r="E31">
+        <v>35.78947</v>
+      </c>
+      <c r="F31">
         <v>66.45963</v>
       </c>
-      <c r="D31">
+      <c r="G31">
         <v>100.4695</v>
       </c>
-      <c r="E31">
-        <v>96.24413</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>93.54839</v>
       </c>
-      <c r="G31">
-        <v>78.22581</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>50.52632</v>
-      </c>
-      <c r="I31">
-        <v>35.78947</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:40</t>
+    <t xml:space="preserve">2026-08-02 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:40</t>
+    <t xml:space="preserve">2026-08-05 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:32</t>
+    <t xml:space="preserve">2026-08-05 18:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:14</t>
+    <t xml:space="preserve">2026-08-16 09:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:44</t>
+    <t xml:space="preserve">2026-08-19 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:39</t>
+    <t xml:space="preserve">2026-08-28 11:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:22</t>
+    <t xml:space="preserve">2026-09-06 17:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
